--- a/apps/web/public/importmallar/importmall-resurser.xlsx
+++ b/apps/web/public/importmallar/importmall-resurser.xlsx
@@ -22,7 +22,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Resursens nummer, exakt tre siffror (textformatera kolumnen i Excel så att 110 inte blir 110,0 och 007 inte 7). Finns numret redan uppdateras resursen; används det av en legoresurs blir raden ett fel — den importeras på fliken Legoresurser.</t>
+          <t xml:space="preserve">Obligatorisk. Resursens nummer, tre siffror. 1–2 siffror fylls ut med nollor (7 blir 007). Finns numret redan uppdateras resursen; används det av en legoresurs blir raden ett fel — den importeras på fliken Legoresurser.</t>
         </r>
       </text>
     </comment>
@@ -106,7 +106,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -118,7 +118,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -130,7 +130,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ställtid i minuter som föreslås för nya operationer på resursen, decimalkomma eller punkt, aldrig negativ. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ställtid i minuter, decimalkomma eller punkt, aldrig negativ. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -142,7 +142,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Operationsnamn som föreslås för nya operationer på resursen, max 100 tecken. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Operationsnamn, max 100 tecken. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -206,6 +206,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -217,10 +218,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -326,88 +327,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resursens nummer, exakt tre siffror (textformatera kolumnen i Excel så att 110 inte blir 110,0 och 007 inte 7). Finns numret redan uppdateras resursen; används det av en legoresurs blir raden ett fel — den importeras på fliken Legoresurser.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namn</t>
+          <t xml:space="preserve">Nummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resursens namn, max 100 tecken. Krävs för nya resurser. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Resursens nummer, tre siffror. 1–2 siffror fylls ut med nollor (7 blir 007). Finns numret redan uppdateras resursen; används det av en legoresurs blir raden ett fel — den importeras på fliken Legoresurser.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laserskärning</t>
+          <t xml:space="preserve">110</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typ</t>
+          <t xml:space="preserve">Namn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -417,19 +403,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maskin eller Personal (även Manuellt arbete). Lego, Underleverantör eller Extern hoppar över raden med hänvisning till fliken Legoresurser. Ett okänt ord ger Maskin för nya resurser och lämnar befintliga orörda, med en varning; tom cell likaså utan varning.</t>
+          <t xml:space="preserve">Resursens namn, max 100 tecken. Krävs för nya resurser. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maskin</t>
+          <t xml:space="preserve">Laserskärning</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avdelning</t>
+          <t xml:space="preserve">Typ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -439,19 +425,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Koden på den produktionsgrupp resursen tillhör, max 20 tecken (skiftlägesokänsligt). En okänd kod skapas som ny produktionsgrupp, med Avdelningens namn eller koden som namn. Tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Maskin eller Personal (även Manuellt arbete). Lego, Underleverantör eller Extern hoppar över raden med hänvisning till fliken Legoresurser. Ett okänt ord ger Maskin för nya resurser och lämnar befintliga orörda, med en varning; tom cell likaså utan varning.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PV</t>
+          <t xml:space="preserve">Maskin</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avdelningens namn</t>
+          <t xml:space="preserve">Avdelning</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -461,19 +447,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Produktionsgruppens namn, max 100 tecken — används bara när gruppen skapas av importen; en befintlig grupp byter inte namn.</t>
+          <t xml:space="preserve">Koden på den produktionsgrupp resursen tillhör, max 20 tecken (skiftlägesokänsligt). En okänd kod skapas som ny produktionsgrupp, med Avdelningens namn eller koden som namn. Tom cell lämnar fältet orört.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plåtverkstad</t>
+          <t xml:space="preserve">PV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timkostnad</t>
+          <t xml:space="preserve">Avdelningens namn</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -483,19 +469,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resursens kostnad per timme i SEK, decimalkomma eller punkt, aldrig negativ — används i för- och efterkalkylen. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Produktionsgruppens namn, max 100 tecken — används bara när gruppen skapas av importen; en befintlig grupp byter inte namn.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950</t>
+          <t xml:space="preserve">Plåtverkstad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalkylpris 1</t>
+          <t xml:space="preserve">Timkostnad</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -505,19 +491,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alternativt timpris i SEK, decimalkomma eller punkt, aldrig negativt. Sparas på resursen men används inte av kalkylen ännu.</t>
+          <t xml:space="preserve">Resursens kostnad per timme i SEK, decimalkomma eller punkt, aldrig negativ — används i för- och efterkalkylen. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900</t>
+          <t xml:space="preserve">950</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gäller ställ</t>
+          <t xml:space="preserve">Kalkylpris 1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -527,19 +513,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Alternativt timpris i SEK, decimalkomma eller punkt, aldrig negativt. Sparas på resursen men används inte av kalkylen ännu.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">900</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gäller styck</t>
+          <t xml:space="preserve">Gäller ställ</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -549,7 +535,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -561,7 +547,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Förvald ställtid</t>
+          <t xml:space="preserve">Gäller styck</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -571,19 +557,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ställtid i minuter som föreslås för nya operationer på resursen, decimalkomma eller punkt, aldrig negativ. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Förvald operationsbenämning</t>
+          <t xml:space="preserve">Förvald ställtid</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -593,32 +579,54 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operationsnamn som föreslås för nya operationer på resursen, max 100 tecken. Sparas som förvalsvärde; tom cell lämnar fältet orört.</t>
+          <t xml:space="preserve">Ställtid i minuter, decimalkomma eller punkt, aldrig negativ. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laserskärning</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Förvald operationsbenämning</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operationsnamn, max 100 tecken. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laserskärning</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kostnadsrad</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Styrkolumn för filer med flera kostnadsrader per resurs: bara raden vars värde börjar med Ordinarie importeras; saknar resursen en sådan tas dess första rad med en varning. Lagras inte — ta bort kolumnen när filen har en rad per resurs.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordinarie</t>
         </is>

--- a/apps/web/public/importmallar/importmall-resurser.xlsx
+++ b/apps/web/public/importmallar/importmall-resurser.xlsx
@@ -106,11 +106,23 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Ett andra alternativt timpris i SEK, decimalkomma eller punkt, aldrig negativt. Sparas på resursen men används inte av kalkylen ännu.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -134,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -146,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -227,9 +239,10 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -270,25 +283,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kalkylpris 2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gäller ställ</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gäller styck</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förvald ställtid</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förvald operationsbenämning</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kostnadsrad</t>
         </is>
@@ -525,7 +543,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gäller ställ</t>
+          <t xml:space="preserve">Kalkylpris 2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -535,19 +553,19 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ett andra alternativt timpris i SEK, decimalkomma eller punkt, aldrig negativt. Sparas på resursen men används inte av kalkylen ännu.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gäller styck</t>
+          <t xml:space="preserve">Gäller ställ</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -557,7 +575,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller ställtiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -569,7 +587,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Förvald ställtid</t>
+          <t xml:space="preserve">Gäller styck</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -579,19 +597,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ställtid i minuter, decimalkomma eller punkt, aldrig negativ. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — om timkostnaden gäller stycktiden. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Förvald operationsbenämning</t>
+          <t xml:space="preserve">Förvald ställtid</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -601,32 +619,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operationsnamn, max 100 tecken. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ställtid i minuter, decimalkomma eller punkt, aldrig negativ. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laserskärning</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Förvald operationsbenämning</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operationsnamn, max 100 tecken. Sparas på resursen som förvalsvärde; används inte av beredningen eller kalkylen ännu. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laserskärning</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kostnadsrad</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Styrkolumn för filer med flera kostnadsrader per resurs: bara raden vars värde börjar med Ordinarie importeras; saknar resursen en sådan tas dess första rad med en varning. Lagras inte — ta bort kolumnen när filen har en rad per resurs.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ordinarie</t>
         </is>
